--- a/downloaded_pdfs/template_updated.xlsx
+++ b/downloaded_pdfs/template_updated.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="16.5" customWidth="1" min="1" max="1"/>
@@ -2446,17 +2446,9 @@
       <c r="K30" t="n">
         <v>250000</v>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>250000</v>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>FBIU0477012</t>
@@ -2465,6 +2457,462 @@
       <c r="V30" t="inlineStr">
         <is>
           <t>Container 20 feet hàng khô</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>202509338904</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CL014920</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VETC</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BLHPH005236/25</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>BLHPH005236/25/1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>B_EWF</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>EXPRESS WAY FEES</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>shipment</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>250000</v>
+      </c>
+      <c r="M31" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>FBIU0477012</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Container 20 feet hàng khô</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>202509336636</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CL014920</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VETC</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BLHPH005504/25</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NSSLKYHPC2500039</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>B_EWF</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>EXPRESS WAY FEES</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>shipment</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>250000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Đồng/Container</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Đồng/Container</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>202509336636</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CL014920</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VETC</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BLHPH005504/25</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NSSLKYHPC2500039</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>B_EWF</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>EXPRESS WAY FEES</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>shipment</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>250000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Đồng/Container</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Đồng/Container</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>202509336636</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CL014920</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VETC</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BLHPH005504/25</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NSSLKYHPC2500039</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>B_EWF</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>EXPRESS WAY FEES</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>shipment</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>250000</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Đồng/Container</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Đồng/Container</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>202509336636</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CL014920</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VETC</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BLHPH005504/25</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NSSLKYHPC2500039</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>B_EWF</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>EXPRESS WAY FEES</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>shipment</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>250000</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Đồng/Container</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Đồng/Container</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>202509336636</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CL014920</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VETC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BLHPH005504/25</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NSSLKYHPC2500039</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>B_EWF</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>EXPRESS WAY FEES</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>shipment</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>250000</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Đồng/Container</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Đồng/Container</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>202509336636</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CL014920</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VETC</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BLHPH005504/25</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NSSLKYHPC2500039</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>B_EWF</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>EXPRESS WAY FEES</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>shipment</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Đồng/Container</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Đồng/Container</t>
         </is>
       </c>
     </row>

--- a/downloaded_pdfs/template_updated.xlsx
+++ b/downloaded_pdfs/template_updated.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="16.5" customWidth="1" min="1" max="1"/>
@@ -2446,23 +2446,87 @@
       <c r="K30" t="n">
         <v>250000</v>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>250000</v>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>FBIU0477012</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
+        <is>
+          <t>Container 20 feet hàng khô</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>202509338904</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CL014920</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VETC</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BLHPH005236/25</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>BLHPH005236/25/1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>B_EWF</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>EXPRESS WAY FEES</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>shipment</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>250000</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>FBIU0477012</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
         <is>
           <t>Container 20 feet hàng khô</t>
         </is>
